--- a/data/trans_dic/IP31KM02_R_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM02_R_2023-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>15,26%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,15; 29,82</t>
+          <t>8,31; 23,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,17; 25,8</t>
+          <t>9,24; 24,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,39; 25,01</t>
+          <t>10,5; 21,03</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>50,41%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>51,58%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>50,95%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,45; 57,2</t>
+          <t>40,83; 59,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>41,25; 59,42</t>
+          <t>42,72; 60,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32,54; 54,91</t>
+          <t>44,19; 57,46</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>58,4%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>54,67%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41,32; 62,47</t>
+          <t>48,47; 69,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>46,77; 67,22</t>
+          <t>39,87; 60,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>47,28; 62,17</t>
+          <t>47,24; 61,97</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>74,5%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,47%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>63,04; 82,52</t>
+          <t>60,44; 85,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>62,46; 86,95</t>
+          <t>65,08; 83,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66,57; 82,04</t>
+          <t>65,58; 81,33</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>90,89; 100,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>90,62; 100,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>95,6; 100,0</t>
+          <t>95,78; 100,0</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>43,72%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>28,51; 50,85</t>
+          <t>38,05; 59,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>38,4; 60,61</t>
+          <t>28,29; 49,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>36,89; 52,17</t>
+          <t>36,03; 51,85</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>73,5%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>71,94; 84,52</t>
+          <t>61,27; 77,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>65,04; 79,84</t>
+          <t>69,59; 83,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>69,41; 80,27</t>
+          <t>67,55; 78,43</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>88,48%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>78,21; 89,95</t>
+          <t>87,18; 95,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>87,27; 94,94</t>
+          <t>76,98; 90,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>84,95; 91,87</t>
+          <t>84,16; 91,78</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>65,91%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>53,57; 66,46</t>
+          <t>63,43; 70,06</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>62,13; 69,39</t>
+          <t>61,57; 68,01</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>60,07; 66,82</t>
+          <t>63,46; 68,21</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12991</t>
+          <t>8967</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11929</t>
+          <t>8606</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24921</t>
+          <t>17572</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7248; 21294</t>
+          <t>5008; 14151</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6842; 19246</t>
+          <t>5075; 13297</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16635; 36515</t>
+          <t>12090; 24218</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>73</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>53620</t>
+          <t>57944</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>63950</t>
+          <t>51233</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>117570</t>
+          <t>109176</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23177; 71868</t>
+          <t>46929; 68516</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>52149; 75122</t>
+          <t>42433; 60278</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>82012; 138413</t>
+          <t>94690; 123136</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>47</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>28678</t>
+          <t>33464</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>37427</t>
+          <t>27447</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66105</t>
+          <t>60911</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>22956; 34702</t>
+          <t>27772; 39763</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>30226; 43443</t>
+          <t>21575; 32559</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>56825; 74720</t>
+          <t>52631; 69037</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>68</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>51527</t>
+          <t>51969</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>56902</t>
+          <t>52496</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>108429</t>
+          <t>104465</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>43930; 57501</t>
+          <t>42197; 59469</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>47075; 65529</t>
+          <t>45854; 58754</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>96566; 119002</t>
+          <t>91999; 114083</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>65</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>39579</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>34566</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>74052</t>
+          <t>74145</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>31085; 34200</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>32054; 35370</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>71625; 74919</t>
+          <t>71784; 74949</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>29</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>17156</t>
+          <t>22930</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>26383</t>
+          <t>17072</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>43538</t>
+          <t>40002</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>12626; 22522</t>
+          <t>17964; 28285</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>20653; 32595</t>
+          <t>12530; 22087</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>36182; 51168</t>
+          <t>32964; 47437</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>136</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>133</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>96942</t>
+          <t>99553</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>113407</t>
+          <t>93318</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>210350</t>
+          <t>192872</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>88982; 104548</t>
+          <t>86128; 109226</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>100834; 123780</t>
+          <t>84777; 101263</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>193480; 223748</t>
+          <t>177243; 205790</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>161</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>109769</t>
+          <t>144598</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>141770</t>
+          <t>116455</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>251539</t>
+          <t>261053</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>100624; 115737</t>
+          <t>136991; 149708</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>134532; 146358</t>
+          <t>106156; 124536</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>240263; 259826</t>
+          <t>248299; 270785</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>594</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>404017</t>
+          <t>459003</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>492487</t>
+          <t>401193</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>896504</t>
+          <t>860195</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>349862; 434069</t>
+          <t>435647; 481165</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>462686; 516775</t>
+          <t>380651; 420442</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>839638; 934115</t>
+          <t>828113; 890164</t>
         </is>
       </c>
     </row>
